--- a/校园招聘/制造业/制造业通用/技术研发类/机械工程师/4_需重新出答案/4轮_制造业通用_机械工程师_重新出答案.xlsx
+++ b/校园招聘/制造业/制造业通用/技术研发类/机械工程师/4_需重新出答案/4轮_制造业通用_机械工程师_重新出答案.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,21 +489,9 @@
           <t>在轴类零件加工中，图纸要求某段外圆柱面轴线相对于基准A（另一段外圆柱面）的同轴度公差为Φ0.02mm；实际检测时，操作人员将零件装夹在V型块上，以基准A为回转轴线，测量该外圆柱面的径向圆跳动值为0.018mm。请问该测量结果能否充分保证同轴度要求得到满足？请简述原因。</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>不能充分保证。因为径向圆跳动是在零件绕基准A旋转时测得的表面各点到回转中心的最大距离差，它同时包含了同轴度误差和被测圆柱面自身的圆度误差；而同轴度只控制被测轴线与基准轴线之间的位置偏差，不包含形状误差。当圆度误差存在时，即使圆跳动合格，同轴度也可能超差。</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>工程上常用三种检测方案：一是三坐标测量机打点拟合两轴线计算同轴度，精度高但耗时长、需编程；二是采用高精度同心套+指示表在车床或专用检具上模拟基准回转，效率高且贴近工艺状态，适合批量现场判定；三是用V型块配合回转台测圆跳动作间接评估，成本低但仅能提供保守下限——即圆跳动合格时同轴度未必合格，反之则一定不合格。综合时效性、现场适配性和判定可靠性，第二种方案是机械工程师在产线首件确认和过程巡检中最常选用的主流方法。</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1个异常情况概要：V型块装夹导致基准A实际回转轴线偏移。具体情况：基准A表面存在局部磕碰、毛刺或V型块定位面磨损，使零件在旋转中产生微小摆动，造成圆跳动读数虚低，掩盖真实同轴度偏差。解决思路：检测前必须确认V型块定位面状态，并用千分表复核基准A自身径向跳动是否≤0.005mm。1个复杂问题概要：被测段与基准A之间存在较长悬臂或中间键槽/退刀槽削弱刚性。具体问题：旋转测量时该段因弹性变形产生附加跳动，使圆跳动值失真，无法反映静态几何同轴关系。解决思路：改用两点支撑式专用检具约束中间段刚性，或在设计阶段明确标注‘检测时需增加辅助支撑’并纳入工艺文件管控。</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>工程图与公差</t>
@@ -548,21 +536,9 @@
           <t>在汽车发动机缸体上，气缸孔的位置度公差标注在相对于主轴承孔轴线和底面的基准体系下，这个位置度要求主要保障气缸与曲轴之间的哪种装配关系？请简述其对整机运行的影响。</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>该位置度要求主要保障气缸中心线与曲轴旋转中心线的同轴关系。这是通过将主轴承孔轴线作为第一基准（控制曲轴安装基准）、底面作为第二基准（控制缸体安装姿态和高度方向约束）所建立的基准体系来实现的。只有保证气缸孔轴线在该基准系下的理论正确位置，才能使活塞连杆组件在往复运动过程中始终沿曲轴旋转中心线的法向轨迹运动，从而形成稳定的运动学匹配。</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>工程实践中主要有三种常用方案：一是采用三坐标测量机配合专用夹具进行单件全尺寸检测，优势是数据全面、可追溯，但节拍慢、成本高，适用于试制和问题排查；二是使用组合式气动量仪+基准模拟芯棒进行在线快速检测，优势是效率高、适合产线节拍，但仅能测径向偏移，无法识别角度偏差；三是基于激光跟踪仪+数字化装配仿真反馈闭环，优势是能关联加工误差与装配变形，但依赖建模精度和现场标定稳定性。综合制造节拍、检测覆盖性与产线适配性，当前主流量产线优先选用第二种方案，并辅以第一种做周期性能力验证。</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>1个异常情况概要：批量检测中发现气缸孔位置度超差但主轴承孔合格。具体情况：缸体粗加工后底面平面度超差，导致基准转换时底面模拟失效，使位置度评价失真。解决思路：在夹具设计阶段增加底面三点浮动支撑补偿机构，并在过程检验中增设底面平面度前置管控点。1个复杂问题概要：热处理后缸体变形导致位置度实测值系统性偏移。具体问题：铝合金缸体T6处理后底面与主轴承孔基准联动变形，造成基准体系失稳，位置度统计过程能力CPK持续低于1.33。解决思路：引入工艺仿真驱动的补偿加工策略，在精镗前基于变形预测模型反向修正刀具路径，并同步优化时效处理工序的装夹刚性和冷却均匀性。</t>
-        </is>
-      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>工程图与公差</t>
@@ -607,21 +583,9 @@
           <t>在车床主轴箱体与端盖装配时，轴向间隙由三个零件的厚度尺寸链决定，若所有组成环都按极值法标注公差，当实测各零件尺寸均处于各自公差带内但间隙仍超差，这反映了极值法对实际装配结果的哪类风险预估？请简述。</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>这反映了极值法对实际装配结果中‘尺寸实际分布状态不可控’这一风险缺乏预估。极值法假设每个组成环尺寸都以最不利方向同时达到极限偏差，从而计算出间隙的最大可能变动范围；但它未考虑各零件尺寸在公差带内的实际分布规律，也未反映制造过程中尺寸偏态、集中或相关性等统计特性，因此无法体现真实装配中多数情况偏离极端组合的客观事实。</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>当前工程实践中主要有三种替代或补充方案：一是采用统计公差法，基于过程能力数据评估尺寸自然波动，能更贴近量产实际，但要求稳定的过程能力且需定期验证，适用于批量稳定的成熟产线；二是引入修配法，在装配现场通过刮研或垫片调整间隙，响应快、不依赖前期公差收紧，但增加人工工时和检测环节，适合单件小批高精度装备；三是改用RSS根方和法进行公差分配，在保证可靠性的前提下放宽单件公差，平衡制造成本与装配合格率，是目前主流设计阶段首选。综合来看，RSS法在时效性、可实施性和成本控制上最为均衡，已成为新机型设计阶段的常规做法。</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>1个异常情况概要：装配后间隙忽大忽小，同一批次产品离散度高；具体情况：三个厚度尺寸的实际加工均值存在系统性偏移（如刀具磨损导致某零件持续偏厚），但仍在公差带内，造成间隙整体右偏甚至超上限；解决思路：在工艺策划阶段识别关键尺寸链组成环，对易偏移工序增设首末件比对与过程均值监控，而非仅依赖终检合格判定。1个复杂问题概要：多批次装配合格率突然下降，但所有零件抽检尺寸全合格；具体问题：箱体与端盖接触面平面度退化引发局部干涉，使有效厚度链传递失真，间隙测量值不能真实反映轴向约束状态；解决思路：将平面度、表面粗糙度等形位公差纳入尺寸链敏感度分析，对配合面设定装配前接触率检查项，并在试装阶段增加模拟载荷下的间隙复测环节。</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>工程图与公差</t>
@@ -666,21 +630,9 @@
           <t>冲孔边距的最小推荐值通常与哪个材料参数直接相关？</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>冲孔边距的最小推荐值通常与材料的抗剪强度直接相关。抗剪强度决定了材料在冲裁过程中抵抗边缘撕裂或开裂的能力，是工艺规范中设定边距下限的核心力学依据。</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>在实际工程中，常用三种技术方案确定边距：一是查企业级钣金工艺手册，按材料牌号和厚度查表取值，优点是响应快、适配产线设备，但未考虑批次性能波动；二是依据GB/T 30573-2014《金属材料 钣金成形工艺性评价方法》中抗剪强度实测值反推边距，精度高但耗时长，适用于首件验证或高可靠性产品；三是调用PLM系统内置的材料数据库，自动关联供应商提供的热轧/冷轧态抗剪强度区间，兼顾时效性与批次一致性，是当前主流产线采用的方式。综合来看，第三种方式最平衡——既满足批量交付节奏，又避免因材料状态（如冷硬程度）变化导致边距不足引发废品。</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>1个异常情况概要：冲孔后边缘微裂纹未被检出。具体情况：某批SPCC冷轧板抗剪强度实测值比标称低8%，但未触发来料复检，冲孔边距按常规值设定，导致装配后振动工况下裂纹缓慢扩展。解决思路：将抗剪强度偏差超±5%纳入IQC必控项，并在冲孔工序后增加10倍放大镜抽检关键边距区域。1个复杂问题概要：异种材料叠压冲孔时边距失效。具体问题：不锈钢304与铝6061叠料冲孔，两者抗剪强度差异大，铝侧易撕裂而钢侧无变形，传统单值边距无法适配。解决思路：按叠层中抗剪强度最低层材料单独核算边距，并在工艺文件中明确标注‘以薄弱层为准’，同时在模具设计阶段增加局部压料力补偿结构。</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>制造工艺</t>
@@ -722,37 +674,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>在机械加工现场，图纸上一个焊缝符号的基准线没有虚线，实心箭头指向接头一侧，且基准线上方标注‘3’、下方标注‘6’。请简述这个符号所表示的焊缝类型、两侧焊脚尺寸要求及施焊时应关注的结构对称性问题。</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>这是一个单边V型坡口角焊缝符号，实心箭头指向的一侧是施焊侧，需焊出焊脚尺寸为6毫米；另一侧（非箭头侧）是未开坡口的母材侧，对应焊脚尺寸为3毫米；基准线无虚线说明该焊缝仅在箭头侧施焊，不要求双侧对称焊接。</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>实际工程中常采用三种工艺方案：一是分道多层手工电弧焊，适合小批量且空间受限场景，但易产生角变形，需频繁校正；二是带衬垫的单面气体保护焊，效率高、熔深可控，但对装配间隙和衬垫贴合度敏感；三是预置反变形+定位焊固定后单面焊接，兼顾精度与效率，适用于中厚板结构件。综合时效性、质量稳定性和现场适配性，第三种方案最常用——它通过提前预估收缩量控制形变，在保证焊缝成形的同时，避免后续矫形返工，符合机械工程师对制造过程可控性的核心要求。</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>1个异常情况概要：焊后单侧角变形超差；具体情况：因6毫米侧热输入集中、冷却收缩不均，导致构件平面度或装配接口错位；解决思路：在焊接前按经验系数加放反变形量，并用刚性工装压紧关键基准面，焊接后优先检测装配面而非仅测焊脚尺寸。1个复杂问题概要：异种厚度板对接时焊脚尺寸公差难协调；具体问题：3毫米侧母材较薄，按标准施焊易烧穿或热影响区脆化；解决思路：将3毫米侧焊脚尺寸实际执行为‘最小可成形尺寸’（通常取2.5毫米），同时调整该侧焊接参数降低热输入，并在工艺文件中注明‘以不烧穿、无咬边为验收前提’，由工艺员与质检联合确认。</t>
-        </is>
-      </c>
+          <t>在机械零部件需要兼顾耐磨性和抗腐蚀性时，为什么通常会优先选择镀硬铬而不是普通电镀锌？请简单说说关键原因。</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>制造工艺</t>
+          <t>机械设计基础</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>焊接工艺</t>
+          <t>材料工艺理解</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>焊缝符号表达</t>
+          <t>表面处理工艺选择</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -781,37 +721,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>审查一份压力容器部件图纸时，看到焊缝符号基准线上方标注‘BW’、下方标注‘8’，且无虚线和箭头折线。请简单说说‘BW’代表的焊接方法类别，该标注对焊缝成型位置和坡口加工方式提出了什么基本要求。</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>‘BW’是埋弧焊的缩写，属于熔化极自动或半自动焊接方法类别。标注在基准线上方，说明焊缝位于箭头所指一侧；下方数字‘8’表示焊缝有效厚度为8毫米；无虚线和箭头折线，表明该焊缝为双面连续角焊缝或对接焊缝，且无需区分施焊侧与非施焊侧，即要求两侧均需加工坡口并完成焊接。</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>针对该BW+8标注，实际制造中常见三种坡口方案：一是单边V型坡口配背面清根，适合中厚板但增加清根工序和检测成本；二是双边V型对称坡口，可减少变形、免清根，但需双侧机加工，对工装定位精度要求高；三是U型坡口，热输入更均匀、残余应力小，但加工成本高、周期长。综合考虑压力容器对强度一致性、无损检测覆盖率及批量制造效率的要求，双边V型坡口是最优选择——它兼顾了焊缝熔透可靠性、坡口加工经济性、组对刚性控制，也便于射线检测布置，符合JB/T 4709标准对受压元件全焊透接头的基本工艺导向。</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>1个异常情况概要：焊缝局部未熔合。具体情况：现场发现BW焊缝在8mm厚度区域出现间断性未熔合，尤其集中在引弧/收弧段，且母材为Q345R，坡口角度符合图纸但钝边略超2mm。解决思路：立即暂停施焊，核查焊接电流电压匹配性、焊丝干伸长稳定性及引弧板安装状态；同步复测坡口钝边尺寸，超差处返修加工，并在后续焊道增加引弧板预热和收弧填弧操作要求。1个复杂问题概要：筒体环焊缝因结构刚性导致角变形超差。具体问题：BW焊缝施焊后实测筒体圆度偏差达2.5mm，超出GB/T 150.4允许的1.5mm限值，影响后续封头装配间隙。解决思路：优化焊接顺序，采用分段退焊+刚性拘束工装；在坡口加工阶段预留反变形量（按经验预设0.8°），并在首件试焊后实测变形趋势，动态调整工艺参数和约束力分布。</t>
-        </is>
-      </c>
+          <t>若一个紧固螺栓在装配后长期承受静载拉伸力，且服役环境存在轻微腐蚀，那么在评估其安全系数时，除材料屈服强度外，还应考虑哪类强度指标？为什么？</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>制造工艺</t>
+          <t>机械设计基础</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>焊接工艺</t>
+          <t>机构与载荷分析</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>焊缝符号表达</t>
+          <t>安全系数与失效模式关系</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -840,42 +768,30 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>一张钢结构连接件图纸中，焊缝符号基准线上方标注‘C’、下方标注‘10’，且基准线末端带圆形封闭标记。请简单说说‘C’在此处代表的接头形式含义，该标注对装配间隙控制和焊接顺序安排提出了什么基础性工艺约束。</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>‘C’代表单边V形坡口接头，这是国标GB/T 324—2022《焊缝符号表示法》中明确定义的标准化代号。基准线上方‘C’表示坡口开在箭头所指一侧的母材上，下方‘10’表示坡口深度为10毫米，圆形封闭标记表明该焊缝需全周连续施焊。这一标注直接限定了结构必须按单侧开坡口、背面不加衬垫、焊透至根部的设计意图，因此装配时必须确保箭头侧母材预留准确坡口角度与钝边，且对接间隙须严格控制在工艺允许范围内，否则无法保证熔深和背面成形；焊接顺序上必须优先完成该侧坡口填充，不得颠倒施焊方向或跳焊，否则易引发未熔合或根部未焊透。</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>针对该单边V形坡口（C型）接头，常见工艺方案有三种：一是采用手工电弧焊打底+多层多道填充，优势是设备适应性强、便于现场调整，但效率低、热输入波动大，易引致角变形；二是实心焊丝CO2气体保护焊，熔敷效率高、过程稳定，但对装配间隙敏感，间隙超2毫米即易烧穿；三是药芯焊丝气保焊，兼具熔深控制与抗间隙波动能力，尤其适合10mm坡口深度场景，综合良率与节拍最优。三者中，药芯焊丝方案在当前主流钢结构制造中应用最广，因其在保证单面焊双面成形前提下，对装配间隙容差达±1.5毫米，且热输入集中可控，更利于后续矫正与尺寸复检。</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>1个异常情况概要：焊缝根部出现连续性未焊透。具体情况：装配时箭头侧钝边过大或间隙过小，导致电弧无法穿透根部，X射线检测显示焊缝底部存在条状未熔合。解决思路：立即暂停该批次装配，用塞尺复测所有同类接头的钝边与间隙，同步调整焊接参数中的电压与行走速度，并在首件试焊后增加根部着色渗透检测。1个复杂问题概要：多道焊后接头区域出现明显角变形超差。具体问题：因C型坡口单侧施焊热输入不对称，导致构件平面度偏差超出公差±1.5毫米，影响后续机加工定位基准。解决思路：在焊接前增设反变形工装压紧，将理论反变形量按板厚与焊缝长度查表预设；同时将原单向连续焊改为分段退步焊，每段≤300毫米，并在每道焊后增加锤击释放应力工序，最后用激光跟踪仪实测变形趋势并动态修正后续焊序。</t>
-        </is>
-      </c>
+          <t>在批量生产的箱体类零件中，端面安装孔组的位置度公差采用最大实体要求（MMR），但实测发现部分零件在功能验证中出现装配干涉。请从位置度与尺寸公差的耦合关系出发，解释这种干涉现象产生的根本原因。</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>制造工艺</t>
+          <t>工程图与公差</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>焊接工艺</t>
+          <t>形位公差应用</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>焊缝符号表达</t>
+          <t>位置度对装配功能的约束</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>中等</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -899,37 +815,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>某核电设备支撑架图纸中，管与法兰环焊缝采用带双引线的焊缝符号：主基准线左侧为直角三角形，引上线'12'，引下线'3×50'；右侧附加一条平行基准线，其上标注'GTAW-2G'并带'F'标记。请简述该复合标注对焊接顺序、填充金属选择及无损检测覆盖范围提出的三重约束条件，并解释为何不能将右侧标注简单理解为‘仅打底用氩弧焊’。</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>该焊缝符号中，直角三角形表示角焊缝，引上线‘12’指焊脚尺寸为12毫米，引下线‘3×50’表示三段间断焊，每段长50毫米、间距未标默认按标准间隔；右侧平行基准线上的‘GTAW-2G+F’明确限定：必须采用钨极惰性气体保护焊（即氩弧焊）在立位固定管轴线的焊接位置（2G），且‘F’标记代表该焊缝全周连续施焊——不是局部或仅打底，而是整圈焊缝均须满足此工艺条件。因此，焊接顺序须先完成GTAW全周焊，不得分层切换工艺；填充金属须匹配GTAW工艺与母材（如核电常用SA-105/SA-336+ER80S-G类焊丝）；无损检测须覆盖整圈焊缝全长，不可因‘打底’概念而缩减检测范围。</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>针对该标注，常见三种执行方案：一是单工艺GTAW全焊道完成，优势是工艺一致性高、热输入可控、缺陷复现率低，但效率偏低、对焊工具备高技能要求；二是GTAW打底+其他工艺盖面，虽提升效率，但违反‘F’标记强制全周GTAW的要求，属图纸不符；三是分段GTAW施焊后整体检测，虽便于过程控制，但‘3×50’为间断焊形式，而主符号为连续角焊缝，二者矛盾需设计澄清——实际工程中必须以主基准线为准，‘3×50’在此处属误标或需技术核定。最优方案是单工艺GTAW全周连续施焊，兼顾图纸合规性、核电设备对焊缝冶金一致性和残余应力分布均匀性的刚性要求。</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>1个异常情况概要：现场发现焊工按‘GTAW-2G’执行时，因管径较小导致熔池观察困难，出现局部未熔合。具体情况：支撑架小直径厚壁管（Φ168×16）立位GTAW操作视野受限，电弧偏吹造成一侧熔深不足。解决思路：机械工程师须协同焊接工艺员调整坡口钝边与间隙，增加内窥辅助定位，而非允许改用其他焊接方法——核心是保障原始符号定义的冶金与力学完整性。1个复杂问题概要：图纸未明确母材热处理状态与焊后是否需PWHT。具体问题：SA-336 Gr.22锻件焊前为正火+回火态，GTAW热输入可能引发HAZ软化，但‘F’标记未关联热处理要求。解决思路：机械工程师须依据RCC-M M篇查证该厚度组合是否触发强制焊后热处理，若需，则在工艺文件中明确PWHT温度窗口与保温时间，并同步更新NDT时机（必须在热处理后执行）</t>
-        </is>
-      </c>
+          <t>在精密装配中，当多个零件通过螺栓孔组连接时，若设计要求所有孔的轴线必须同时落在同一理论位置上，且允许整体偏移但不允许单个孔相对位置失准，此时应如何选择位置度公差的基准体系？请简述理由。</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>制造工艺</t>
+          <t>工程图与公差</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>焊接工艺</t>
+          <t>形位公差应用</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>焊缝符号表达</t>
+          <t>位置度对装配功能的约束</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -958,24 +862,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>某企业为降本将某冲压支架的材料从SPCC冷轧钢替换为DC04，两者标称屈服强度相近，但DC04批次间r值离散度达±0.2。请说明该塑性参数波动会如何传导至材料利用率、废品率及边角料价值三个环节，并指出在启动批量切换前，成本评估必须补充验证的两个关键工艺实测数据。</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>r值反映材料在拉伸时宽向与厚向应变的比值，直接影响板料在冲压成形中抵抗变薄和起皱的能力。r值波动±0.2意味着同一批次材料各卷之间塑性各向异性差异显著：r值偏低时材料更易局部变薄甚至开裂，r值偏高时则更易起皱或侧向流动失控。这种波动会直接导致同一套模具在不同材料批次上表现出不一致的成形稳定性，进而影响材料裁剪布局、成形合格状态和余料形态。</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>针对该场景，常用验证方案有三类：一是仅做单点r值送检，优点是快但无法反映整卷波动，易漏判风险；二是按标准取3个位置（头、中、尾）测r值并记录极差，能识别批次内趋势，但未关联实际成形结果；三是结合模具做小批量试冲，同步采集首件合格率、修边余量偏差和边角料厚度分布，时效略长但数据可直接用于成本建模。最优方案是第三种，因为它把r值波动与真实产线节拍、模具磨损、调机频次等工程变量绑定，确保成本评估不脱离制造现场实际。</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>1个异常情况概要：冲压首件合格，但连续生产50件后废品率陡升。具体情况：因DC04某卷r值偏低且表面粗糙度偏高，导致拉延过程中摩擦状态突变，板料局部减薄加速，模具未及时补偿。解决思路：在换卷交接点增设首中末件厚度扫描和目视褶皱复检，将材料批次号与当班废品记录绑定追溯。1个复杂问题概要：边角料称重价值上升但整体材料成本未降。具体问题：r值偏高批次成形时侧向流动加剧，修边余量增大且切边毛刺增多，导致边角料含油量和铁屑比例升高，回收商拒收或折价。解决思路：在试冲阶段同步测量修边件轮廓偏差和断面毛刺高度，将边角料交付品质指标纳入材料切换准入条件。</t>
-        </is>
-      </c>
+          <t>当图纸标注某配合孔为φ25H6，而实际加工后测得尺寸为φ25.012mm，该孔是否合格？请结合公差带定义说明判断依据。</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>制造工艺</t>
@@ -983,17 +875,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>制造成本评估</t>
+          <t>机加工适配</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>材料成本影响</t>
+          <t>孔轴加工精度</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1017,37 +909,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>在机械零部件需要兼顾耐磨性和抗腐蚀性时，为什么通常会优先选择镀硬铬而不是普通电镀锌？请简单说说关键原因。</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>因为镀硬铬层硬度高、致密性好，能同时提供显著的表面耐磨能力和较好的耐介质腐蚀能力；而普通电镀锌层较软、孔隙率高，主要起牺牲阳极保护作用，耐磨性差，且在潮湿或含盐环境中易出现白锈甚至局部穿孔，无法满足耐磨与抗腐蚀双重需求。</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>实际选型中常对比三种方案：一是普通电镀锌，成本低、工艺成熟，但锌层硬度仅80～120HV，摩擦下易刮伤，且无自修复能力，腐蚀防护寿命短；二是镀镍，硬度200～400HV，耐蚀性优于锌，但耐磨性仍不足，且镀层易产生内应力导致微裂纹，在交变载荷下易剥落；三是镀硬铬，硬度达800～1000HV，表面致密无孔，既抵抗磨粒磨损又隔绝腐蚀介质，特别适合承受滑动摩擦和弱酸碱环境的轴类、活塞杆等承力件。综合结构承载要求、服役工况稳定性及后期维护成本，镀硬铬是当前制造业中兼顾两项性能最稳妥的工程选择。</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>1个异常情况概要：镀硬铬后出现微裂纹并加速局部腐蚀。具体情况：某液压缸活塞杆镀硬铬后在湿热环境中服役三个月，铬层表面出现细网状裂纹，裂纹处基体钢发生点蚀。解决思路：核查镀前基体粗糙度是否超Ra0.8μm，确认镀液温度与电流密度匹配性，必要时增加镀后去氢烘烤工序，并评估是否需叠加封闭处理。1个复杂问题概要：在薄壁套筒类零件上实现均匀镀硬铬且不引发变形。具体问题：壁厚2.5mm的不锈钢导向套镀硬铬后圆度超差0.05mm，影响与活塞配合间隙。解决思路：优化装挂方式避免单边受力，控制镀覆过程升温速率，镀后增加时效稳定处理，并在设计阶段预留镀层厚度引起的尺寸修正量。</t>
-        </is>
-      </c>
+          <t>在实际钣金加工中，如果一块厚度为2毫米的冷轧钢板需要冲直径8毫米的圆孔，靠近板料边缘时，最小安全边距应该控制在多少毫米左右？请简述这个数值的确定依据。</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>机械设计基础</t>
+          <t>制造工艺</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>材料工艺理解</t>
+          <t>钣金工艺</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>表面处理工艺选择</t>
+          <t>冲孔边距控制</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1072,360 +952,6 @@
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>若一个紧固螺栓在装配后长期承受静载拉伸力，且服役环境存在轻微腐蚀，那么在评估其安全系数时，除材料屈服强度外，还应考虑哪类强度指标？为什么？</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>应考虑材料的持久强度，也就是在特定温度和腐蚀环境下、长期静载作用下不发生蠕变断裂或应力腐蚀开裂的最高允许应力值。因为题干明确是‘长期承受静载拉伸力’且‘存在轻微腐蚀’，此时螺栓失效模式已超出常规静强度范畴，屈服强度仅反映短期瞬时承载能力，无法表征时间依赖性与环境协同作用下的承载退化行为。</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>工程上常用三类方案评估：一是查GB/T 3098.1附录中带腐蚀修正因子的持久强度许用值，优势是标准成熟、校核便捷，但仅适用于常见碳钢/合金钢螺栓且腐蚀等级需严格匹配；二是采用ISO 13849推荐的应力腐蚀门槛值法，结合服役周期反推临界应力，优势是兼顾时间与环境耦合效应，但需实测或借用同类工况数据，时效性略低；三是按JB/T 13936开展加速腐蚀+恒载试验获取实测持久强度，优势是结果最贴近真实工况，但周期长、成本高，适用于关键部位首件验证。综合来看，首选第一种——在设计阶段优先采用标准中已给出腐蚀修正系数的持久强度许用值，既满足时效性要求，又覆盖制造、装配、检测全流程可执行性。</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>1个异常情况概要：螺栓表面出现点蚀但未达尺寸报废限值，却提前发生脆性断裂。具体情况：轻微腐蚀环境下，氯离子诱发局部应力集中区萌生亚微米级蚀坑，在长期静载下成为应力腐蚀裂纹源，而常规外观检查和扭矩复检均无法识别。解决思路：在装配后增加荧光渗透检测抽检，并将螺栓批次信息与服役环境pH值、湿度数据绑定存档，用于后续寿命趋势分析。1个复杂问题概要：同一规格螺栓在不同产线装配后，部分批次在6个月后陆续失效。具体问题：热处理回火温度波动±15℃导致晶界碳化物析出不均，加剧腐蚀敏感性，但出厂硬度检测全部合格。解决思路：将回火工艺参数（温度、保温时间、炉内温差）纳入质量放行必控项，对每批次螺栓补充晶间腐蚀倾向快速筛选试验，而非仅依赖硬度和金相抽样。</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>机械设计基础</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>机构与载荷分析</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>安全系数与失效模式关系</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>机械工程师</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>在批量生产的箱体类零件中，端面安装孔组的位置度公差采用最大实体要求（MMR），但实测发现部分零件在功能验证中出现装配干涉。请从位置度与尺寸公差的耦合关系出发，解释这种干涉现象产生的根本原因。</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>最大实体要求下，位置度公差值会随实际孔径增大而放宽，即孔越接近下极限尺寸（最小实体状态），允许的位置偏差越小；孔越接近上极限尺寸（最大实体状态），允许的位置偏差越大。但装配时起定位作用的是孔的实际边界——即由实际尺寸和位置共同形成的‘实效边界’。当多个孔同时处于大尺寸且位置偏移方向一致时，其综合实效边界会整体外扩，导致相邻配合件的螺栓或轴销无法顺利插入，引发干涉。</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>常见应对方案有三种：一是改用零几何公差补偿（即RFS），位置度不随尺寸变化，稳定性高但制造成本上升；二是将位置度与基准关联改为基准体系优化，比如增加第二基准控制旋转自由度，提升孔组整体姿态一致性；三是调整尺寸公差带，收严孔径公差以压缩位置度浮动空间。其中第二种最常用——它不增加检测难度，也不牺牲良率，还能兼顾装配导向性，在箱体类零件批量生产中时效性好、工程落地性强。</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>1个异常情况概要：单个孔尺寸合格但孔组整体实效边界超差。具体情况：某批次孔径均在公差内，但因加工系统性偏移（如夹具重复定位偏差），所有孔位置同向偏大，叠加大尺寸后实效边界整体外扩。解决思路：通过首件三坐标比对基准-孔组矢量关系，识别夹具或程序偏差，而非仅依赖单孔尺寸判定。1个复杂问题概要：多基准耦合下的实效边界传递失稳。具体问题：箱体存在底面、侧面、端面三个功能基准，端面孔组位置度以底面为第一基准，但底面平面度波动影响基准模拟，导致实效边界计算失真。解决思路：在工艺文件中明确基准模拟方式（如三点支撑+浮动约束），并在过程检验中增加基准面与孔组的联合扫描分析，确保基准传递链可控。</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>工程图与公差</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>形位公差应用</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>位置度对装配功能的约束</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>机械工程师</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>在精密装配中，当多个零件通过螺栓孔组连接时，若设计要求所有孔的轴线必须同时落在同一理论位置上，且允许整体偏移但不允许单个孔相对位置失准，此时应如何选择位置度公差的基准体系？请简述理由。</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>应采用单一基准体系，即仅以该孔组所在零件自身的基准面（如装配面或主定位面）作为位置度公差的唯一基准，不引入其他零件或外部坐标系。因为题干明确约束‘允许整体偏移但不允许单个孔相对位置失准’，这本质是控制孔组内部的相对位置关系，而非绝对坐标定位，所以基准必须源自本体、稳定可复现，且不传递装配链误差。</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>常见方案有三种：一是以本体一个高刚性平面为单一基准A；二是以本体两正交平面构成基准体系AB；三是以相邻已加工特征（如销孔）为辅助基准。第一种最合理——单一基准A能避免基准叠加带来的累积误差，符合‘整体可偏移’要求，也便于三坐标检测时一次装夹完成全部孔位评价；第二种虽常见于箱体类零件，但会强制约束旋转自由度，违背‘允许整体偏移’的设计意图；第三种引入关联特征，易受前序工序偏差影响，削弱孔组自身位置关系的独立控制能力。综合制造可行性、检测效率和功能匹配性，单一基准A是最优解。</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>1个异常情况概要：检测时发现单个孔超差，但孔组整体位置趋势一致。具体情况：三坐标按单一基准A评价时，某孔位置度超差，但其余孔均合格，且所有孔中心连线呈平行偏移。解决思路：优先核查该孔局部加工状态——是否钻铰余量不均、刀具让刀或夹紧变形导致单孔轴线歪斜，而非基准或程序问题；暂停批量，复测该孔垂直度与表面粗糙度，确认是否为工序能力异常。1个复杂问题概要：多零件叠装后，理论同轴的孔组在实际装配中出现螺栓预紧困难。具体问题：各零件均按单一基准A合格，但叠装时螺栓无法顺畅穿入，说明孔组间存在微小角度偏差或阶梯式偏移。解决思路：在装配工艺文件中补充‘孔组协调公差带’要求，即在首件装配阶段用通止规+柔性导向芯棒做贯通验证，并将协调结果反向反馈至各零件的基准面平面度与垂直度控制要求，实现从单件合格到系统可装的闭环管控。</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>工程图与公差</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>形位公差应用</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>位置度对装配功能的约束</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>机械工程师</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>某传动支架图纸中，原设计将两处安装孔的基准体系设定为‘一面两销’，现因轻量化需求将其中一销孔改为槽形结构。请简述你如何界定该变更对现有检测工装、产线SPC控制点及最终装配功能的影响，并说明必须开展的变更后验证类型。</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>这个变更本质是基准体系从‘一面两销’降级为‘一面一销一槽’，导致定位自由度减少、重复定位精度下降、基准传递路径改变。需据此评估检测工装是否仍能复现原定位状态，SPC控制点是否仍能稳定采集关键尺寸特征，以及装配时螺栓预紧力分布和支架姿态是否发生偏移。</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>常见应对方案有三种：一是改造现有工装，在槽口位置增加可浮动定位销或弹性压紧块，兼顾槽宽公差与定位刚性，实施快、成本低但对槽宽一致性依赖高；二是重新设计专用工装，采用面-销-槽三点约束并引入槽中心找正机构，定位稳定性好但开发周期长；三是维持原工装但收紧槽宽公差带并增加首件三坐标比对，短期可行但放大制造风险。综合权衡时效性与稳健性，优先选用第一种方案，同步补充槽宽过程能力分析和首件装配干涉检查。</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>1个异常情况概要：槽口加工后实际轮廓呈喇叭状或单侧偏磨。具体情况：铣削参数不当或夹具让位不足导致槽口两端深度不一致，造成定位销插入时倾斜，引发工装虚压和检测数据漂移。解决思路：在首件检验中增加槽口两端深度差测量项，并要求机加班组反馈刀具磨损趋势。1个复杂问题概要：装配状态下支架因槽口间隙累积导致传动轴系同轴度超差。具体问题：槽宽公差叠加销轴公差与安装面平面度误差，使支架在螺栓预紧过程中产生微转动，影响后续齿轮啮合间隙。解决思路：开展装配状态下的刚体运动仿真，结合实测槽口-销轴配合间隙分布，重新分配关键尺寸公差链，并在SPC中将‘装配后轴向偏移量’设为新增控制点。</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>工程图与公差</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>设计变更表达</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>变更前后验证要求</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>机械工程师</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>当图纸标注某配合孔为φ25H6，而实际加工后测得尺寸为φ25.012mm，该孔是否合格？请结合公差带定义说明判断依据。</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>H6是基孔制下的标准公差等级，表示基本尺寸φ25的孔，其下偏差为零，上偏差由国家标准查得为+0.013mm，因此公差带范围是φ25.000mm至φ25.013mm。实测值φ25.012mm落在该范围内，属于合格。</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>在机加工现场，判断此类尺寸合格性通常有三种常用方式：一是用数显内径千分尺直接比对上下限值，响应快但依赖操作者读数稳定性；二是用气动量仪做连续监控，适合批量工序，能提前预警趋势但需定期校准基准环规；三是用三坐标测量机做全尺寸报告，精度高、可追溯，但耗时长、成本高，一般用于首件或争议复检。综合时效性、产线适配性和判定权威性，气动量仪配合环规校准是最优方案——它能在加工节拍内完成判定，且与车间日常SPC管控逻辑一致。</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>1个异常情况概要：实测值接近上极限但仍在公差内，但后续装配中出现卡滞或过盈不足。具体情况：该孔需与φ25g6轴配合形成间隙配合，实测φ25.012虽合格，但若轴实际尺寸为φ24.989（下偏差极限），则最小间隙仅0.003mm，易受表面粗糙度或清洁度影响导致装配异常。解决思路：机械工程师需同步核查配套轴的实际测量数据及表面状态，必要时在工艺文件中补充‘间隙验证工装’要求。1个复杂问题概要：同一批次多个H6孔实测均趋近上偏差，但过程能力指数CPK持续低于1.33。具体问题：反映镗孔工序存在系统性偏移或刀具磨损未及时补偿。解决思路：立即暂停加工，调取刀具寿命记录和机床热变形补偿日志，优先排查主轴温升导致的尺寸漂移，并用基准环规做在线补偿验证。</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>制造工艺</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>机加工适配</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>孔轴加工精度</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>机械工程师</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>在实际钣金加工中，如果一块厚度为2毫米的冷轧钢板需要冲直径8毫米的圆孔，靠近板料边缘时，最小安全边距应该控制在多少毫米左右？请简述这个数值的确定依据。</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>对于厚度2毫米的冷轧钢板冲Φ8毫米圆孔，最小安全边距应控制在约10毫米左右。该数值源于行业通用的钣金工艺规范，核心依据是避免冲裁过程中因材料流动和模具侧向力导致边缘开裂、毛刺超标或板料变形，同时保障模具寿命与定位稳定性。</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>目前主流有三种边距控制方案：一是按‘孔径+板厚’经验法，取8+2=10毫米，实施快、适配常规数控冲床，但未考虑材料屈服强度波动；二是参照GB/T 26127—2010《金属薄板冲压工艺规范》推荐值，对冷轧低碳钢（如SPCC、DC01），Φ8孔在2mm厚时明确建议边距不小于1.25倍孔径，即10毫米，标准覆盖了材料成形性与回弹影响，工程接受度高；三是基于模具厂商实测数据库匹配，如通快、村田常用参数库均将该组合标定为9.5～10.5毫米，精度高但依赖供应商协同。综合来看，采用国标推荐的10毫米方案最稳妥——它兼顾制造节拍、检测可复现性及跨设备一致性，且无需额外验证周期，符合机械工程师在量产导入阶段‘控风险、保交付’的核心职责。</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>1个异常情况概要：冲孔后边缘出现微裂纹或局部翘起；具体情况：实际加工中发现距边缘10毫米处Φ8孔边缘有0.1～0.2毫米长度的细小裂纹，伴随孔口一侧轻微鼓起；解决思路：立即暂停批量，核查来料表面质量（是否存在轧制划伤或氧化皮压入），复核冲头刃口垂直度与卸料板压紧力，优先调整卸料间隙至0.03～0.04毫米并增加局部预压痕工序。1个复杂问题概要：同一零件需多工位连续冲压时，首序边距达标但后续折弯导致孔位相对边缘实际距离不足；具体问题：折弯后测量发现Φ8孔到折边距离压缩至7毫米，低于结构刚度要求；解决思路：在工艺策划阶段即开展折弯回弹仿真校核，将初始边距预留加放至11.5毫米，并在折弯模具上设置限位凸台，确保成形后孔边距实测值稳定大于9毫米。</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>制造工艺</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>钣金工艺</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>冲孔边距控制</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>机械工程师</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
